--- a/www/Baseline_Cover_TEMPLATE.xlsx
+++ b/www/Baseline_Cover_TEMPLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\www\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC659CD8-54D9-46A4-BE1A-EF15853E462A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BC0156-503E-4BD5-8D10-24C06B5C9713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3128" yWindow="3128" windowWidth="21600" windowHeight="11332" activeTab="2" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
   <si>
     <t>Acropora cervicornis</t>
   </si>
@@ -355,6 +355,9 @@
   </si>
   <si>
     <t>REQUIRED Unconsolidated substrate</t>
+  </si>
+  <si>
+    <t>REQUIRED Other living benthos</t>
   </si>
 </sst>
 </file>
@@ -921,9 +924,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{101649E4-CD8D-4DAA-89FC-8D6C93B48E30}">
           <x14:formula1>
-            <xm:f>Taxa!$A$2:$A$65</xm:f>
+            <xm:f>Taxa!$A$2:$A$66</xm:f>
           </x14:formula1>
-          <xm:sqref>A3:A1048576 A2</xm:sqref>
+          <xm:sqref>A2:A1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -933,7 +936,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAEEECA6-441C-430E-B4E3-69F7F23BD6EB}">
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
@@ -948,316 +951,321 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A32" s="1" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1268,17 +1276,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="647735499ae6baa62e6fc7f5ed3567b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47ff4a2bf1fedf465812d90a21a07c12" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
@@ -1473,6 +1470,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1483,17 +1491,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
-    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28BE2C18-A8FE-44F8-9370-C2AF79093B54}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1512,6 +1509,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
+    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
   <ds:schemaRefs>
